--- a/data/trans_bre/IP1016-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1016-Edad-trans_bre.xlsx
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-0,53; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
